--- a/docs/d/26/inyear.xlsx
+++ b/docs/d/26/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 68 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 65 clubs short</t>
         </is>
       </c>
     </row>
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5123,8 +5123,8 @@
       <c r="Y43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="9" t="n">
-        <v>0</v>
+      <c r="Z43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA43" s="10" t="n">
         <v>1</v>
@@ -5818,7 +5818,7 @@
         <v>0</v>
       </c>
       <c r="S50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50" s="10" t="n">
         <v>1</v>
@@ -7040,7 +7040,7 @@
         <v>1</v>
       </c>
       <c r="Q62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" s="9" t="n">
         <v>0</v>
@@ -13568,13 +13568,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>0</v>
       </c>
       <c r="V126" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14533,8 +14533,8 @@
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="9" t="n">
-        <v>0</v>
+      <c r="Z135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA135" s="10" t="n">
         <v>1</v>
@@ -14766,7 +14766,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14836,8 +14836,8 @@
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -16188,7 +16188,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -16815,7 +16815,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -16848,7 +16848,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>

--- a/docs/d/26/inyear.xlsx
+++ b/docs/d/26/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,11 @@
       <c r="AB19" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC19" s="4" t="inlineStr"/>
+      <c r="AC19" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -5746,7 +5750,11 @@
       <c r="AB49" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC49" s="4" t="inlineStr"/>
+      <c r="AC49" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -6469,7 +6477,11 @@
       <c r="AB56" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC56" s="4" t="inlineStr"/>
+      <c r="AC56" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -6873,7 +6885,11 @@
       <c r="AB60" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC60" s="4" t="inlineStr"/>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -7792,7 +7808,11 @@
       <c r="AB69" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC69" s="4" t="inlineStr"/>
+      <c r="AC69" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -7893,7 +7913,11 @@
       <c r="AB70" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC70" s="4" t="inlineStr"/>
+      <c r="AC70" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -8200,7 +8224,11 @@
       <c r="AB73" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC73" s="4" t="inlineStr"/>
+      <c r="AC73" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -8301,7 +8329,11 @@
       <c r="AB74" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC74" s="4" t="inlineStr"/>
+      <c r="AC74" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -9432,7 +9464,11 @@
       <c r="AB85" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC85" s="4" t="inlineStr"/>
+      <c r="AC85" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -10854,7 +10890,11 @@
       <c r="AB99" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC99" s="4" t="inlineStr"/>
+      <c r="AC99" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -12199,7 +12239,11 @@
       <c r="AB112" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC112" s="4" t="inlineStr"/>
+      <c r="AC112" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -12405,7 +12449,11 @@
       <c r="AB114" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC114" s="4" t="inlineStr"/>
+      <c r="AC114" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -12708,7 +12756,11 @@
       <c r="AB117" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC117" s="4" t="inlineStr"/>
+      <c r="AC117" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -14239,7 +14291,11 @@
       <c r="AB132" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC132" s="4" t="inlineStr"/>
+      <c r="AC132" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -14340,7 +14396,11 @@
       <c r="AB133" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC133" s="4" t="inlineStr"/>
+      <c r="AC133" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -14542,7 +14602,11 @@
       <c r="AB135" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC135" s="4" t="inlineStr"/>
+      <c r="AC135" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -14643,7 +14707,11 @@
       <c r="AB136" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC136" s="4" t="inlineStr"/>
+      <c r="AC136" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -15253,7 +15321,11 @@
       <c r="AB142" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC142" s="4" t="inlineStr"/>
+      <c r="AC142" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">

--- a/docs/d/26/inyear.xlsx
+++ b/docs/d/26/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 65 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 60 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -918,8 +918,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -1019,8 +1019,8 @@
       <c r="Y3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="9" t="n">
-        <v>0</v>
+      <c r="Z3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA3" s="10" t="n">
         <v>1</v>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="P10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="9" t="n">
         <v>0</v>
@@ -2015,7 +2015,7 @@
         <v>1</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="9" t="n">
         <v>0</v>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
         <v>1</v>
       </c>
       <c r="U17" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V17" s="9" t="n">
         <v>1</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2558,8 +2558,8 @@
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="9" t="n">
-        <v>0</v>
+      <c r="Z18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="P53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" s="9" t="n">
         <v>0</v>
@@ -7012,7 +7012,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7082,8 +7082,8 @@
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="9" t="n">
-        <v>0</v>
+      <c r="Z62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA62" s="10" t="n">
         <v>1</v>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7165,8 +7165,8 @@
       <c r="S63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T63" s="9" t="n">
-        <v>0</v>
+      <c r="T63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U63" s="9" t="n">
         <v>0</v>
@@ -9092,13 +9092,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -10549,7 +10549,7 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q96" s="9" t="n">
         <v>0</v>
@@ -12096,7 +12096,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>0</v>
@@ -12782,7 +12782,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12852,8 +12852,8 @@
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="9" t="n">
-        <v>0</v>
+      <c r="Z118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
@@ -14212,7 +14212,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14226,13 +14226,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>59</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
@@ -14255,8 +14255,8 @@
       <c r="P132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" s="9" t="n">
-        <v>1</v>
+      <c r="Q132" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R132" s="9" t="n">
         <v>0</v>
@@ -14274,7 +14274,7 @@
         <v>4</v>
       </c>
       <c r="W132" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X132" s="10" t="n">
         <v>5</v>
@@ -15050,13 +15050,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
@@ -15799,7 +15799,7 @@
         <v>0</v>
       </c>
       <c r="Q147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R147" s="9" t="n">
         <v>0</v>
@@ -16029,7 +16029,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -16095,7 +16095,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16392,7 +16392,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16788,7 +16788,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -16887,13 +16887,13 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>

--- a/docs/d/26/inyear.xlsx
+++ b/docs/d/26/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 60 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1225,8 +1225,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -1738,8 +1738,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="9" t="n">
         <v>0</v>
@@ -1940,8 +1940,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="9" t="n">
         <v>0</v>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>4</v>
       </c>
       <c r="W15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" s="10" t="n">
         <v>6</v>
@@ -2439,7 +2439,7 @@
         <v>1</v>
       </c>
       <c r="U17" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V17" s="9" t="n">
         <v>1</v>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" s="9" t="n">
         <v>0</v>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2753,8 +2753,8 @@
       <c r="T20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U20" s="9" t="n">
-        <v>0</v>
+      <c r="U20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V20" s="9" t="n">
         <v>0</v>
@@ -2965,7 +2965,7 @@
         <v>0</v>
       </c>
       <c r="X22" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y22" s="9" t="n">
         <v>0</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3075,8 +3075,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3281,8 +3281,8 @@
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3483,8 +3483,8 @@
       <c r="Y27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="n">
-        <v>0</v>
+      <c r="Z27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="10" t="n">
         <v>1</v>
@@ -3669,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="S29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" s="9" t="n">
         <v>0</v>
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4416,8 +4416,8 @@
       <c r="Y36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z36" s="9" t="n">
-        <v>0</v>
+      <c r="Z36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA36" s="10" t="n">
         <v>1</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4517,8 +4517,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4925,8 +4925,8 @@
       <c r="Y41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" s="9" t="n">
-        <v>0</v>
+      <c r="Z41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA41" s="10" t="n">
         <v>1</v>
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -5026,8 +5026,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="10" t="n">
         <v>1</v>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5201,8 +5201,8 @@
       <c r="P44" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" s="9" t="n">
-        <v>1</v>
+      <c r="Q44" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R44" s="9" t="n">
         <v>0</v>
@@ -5228,8 +5228,8 @@
       <c r="Y44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" s="9" t="n">
-        <v>0</v>
+      <c r="Z44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA44" s="10" t="n">
         <v>1</v>
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5333,8 +5333,8 @@
       <c r="Y45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="9" t="n">
-        <v>0</v>
+      <c r="Z45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="10" t="n">
         <v>1</v>
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="9" t="n">
         <v>1</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5741,8 +5741,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6153,8 +6153,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6363,8 +6363,8 @@
       <c r="Y55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z55" s="9" t="n">
-        <v>0</v>
+      <c r="Z55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA55" s="10" t="n">
         <v>1</v>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6674,8 +6674,8 @@
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="9" t="n">
-        <v>0</v>
+      <c r="Z58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7183,8 +7183,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -7438,13 +7438,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
@@ -7483,13 +7483,13 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X66" s="9" t="n">
-        <v>3</v>
+      <c r="X66" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y66" s="9" t="n">
         <v>0</v>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8215,8 +8215,8 @@
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
@@ -8355,7 +8355,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8425,8 +8425,8 @@
       <c r="Y75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z75" s="9" t="n">
-        <v>0</v>
+      <c r="Z75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA75" s="10" t="n">
         <v>1</v>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8721,8 +8721,8 @@
       <c r="T78" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U78" s="9" t="n">
-        <v>0</v>
+      <c r="U78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V78" s="9" t="n">
         <v>3</v>
@@ -8876,7 +8876,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8946,8 +8946,8 @@
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9148,8 +9148,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9284,7 +9284,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9339,8 +9339,8 @@
       <c r="T84" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U84" s="9" t="n">
-        <v>0</v>
+      <c r="U84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V84" s="9" t="n">
         <v>2</v>
@@ -9490,7 +9490,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9560,8 +9560,8 @@
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
@@ -9591,7 +9591,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9661,8 +9661,8 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -9999,7 +9999,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10063,14 +10063,14 @@
       <c r="W91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X91" s="9" t="n">
-        <v>2</v>
+      <c r="X91" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="9" t="n">
-        <v>0</v>
+      <c r="Z91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10114,13 +10114,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -10170,8 +10170,8 @@
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -10205,7 +10205,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10275,8 +10275,8 @@
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA93" s="10" t="n">
         <v>1</v>
@@ -10306,7 +10306,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10376,8 +10376,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -10421,13 +10421,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10780,8 +10780,8 @@
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -10825,13 +10825,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -11845,7 +11845,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11915,8 +11915,8 @@
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
@@ -12475,7 +12475,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12545,8 +12545,8 @@
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -12576,7 +12576,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12646,8 +12646,8 @@
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -12988,7 +12988,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -13029,7 +13029,7 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q120" s="10" t="n">
         <v>2</v>
@@ -13058,8 +13058,8 @@
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13575,8 +13575,8 @@
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="9" t="n">
-        <v>0</v>
+      <c r="Z125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -13808,7 +13808,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13878,8 +13878,8 @@
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
@@ -15930,8 +15930,8 @@
       <c r="Y148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z148" s="9" t="n">
-        <v>0</v>
+      <c r="Z148" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA148" s="9" t="n">
         <v>0</v>
@@ -16029,7 +16029,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -16128,7 +16128,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16161,7 +16161,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -16227,7 +16227,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16260,7 +16260,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -16293,7 +16293,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16326,7 +16326,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16359,7 +16359,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16392,7 +16392,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16458,7 +16458,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16491,7 +16491,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16524,7 +16524,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16557,7 +16557,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16590,7 +16590,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16623,7 +16623,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16656,7 +16656,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -16722,7 +16722,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -16755,7 +16755,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -16788,7 +16788,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -16821,7 +16821,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -16854,7 +16854,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>

--- a/docs/d/26/inyear.xlsx
+++ b/docs/d/26/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/26/inyear.xlsx
+++ b/docs/d/26/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/26/inyear.xlsx
+++ b/docs/d/26/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/26/inyear.xlsx
+++ b/docs/d/26/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/26/inyear.xlsx
+++ b/docs/d/26/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 25 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="P9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="9" t="n">
         <v>0</v>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -2712,13 +2712,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4039,17 +4039,17 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L33" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M33" s="8" t="n">
@@ -4066,7 +4066,7 @@
         </is>
       </c>
       <c r="P33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="9" t="n">
         <v>0</v>
@@ -4080,11 +4080,11 @@
       <c r="T33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U33" s="9" t="n">
-        <v>0</v>
+      <c r="U33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -4665,13 +4665,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         </is>
       </c>
       <c r="P43" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q43" s="9" t="n">
         <v>0</v>
@@ -5170,13 +5170,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5712,8 +5712,8 @@
       <c r="P49" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q49" s="9" t="n">
-        <v>1</v>
+      <c r="Q49" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R49" s="9" t="n">
         <v>0</v>
@@ -6226,7 +6226,7 @@
         <v>1</v>
       </c>
       <c r="Q54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R54" s="9" t="n">
         <v>0</v>
@@ -6511,13 +6511,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>2</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6717,13 +6717,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6761,8 +6761,8 @@
       <c r="U59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V59" s="9" t="n">
-        <v>3</v>
+      <c r="V59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6919,13 +6919,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -7024,13 +7024,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7636,13 +7636,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
@@ -7741,13 +7741,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7947,13 +7947,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7991,8 +7991,8 @@
       <c r="U71" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V71" s="9" t="n">
-        <v>3</v>
+      <c r="V71" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
@@ -8363,13 +8363,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8573,13 +8573,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>4</v>
       </c>
       <c r="W77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X77" s="9" t="n">
         <v>1</v>
@@ -10924,13 +10924,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-18</v>
+        <v>-14</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
@@ -11130,13 +11130,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11441,13 +11441,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>1</v>
@@ -11489,7 +11489,7 @@
         <v>4</v>
       </c>
       <c r="W105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>5</v>
@@ -12063,17 +12063,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L111" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -12469,7 +12469,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12483,13 +12483,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -12527,8 +12527,8 @@
       <c r="U115" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="V115" s="9" t="n">
-        <v>3</v>
+      <c r="V115" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12790,13 +12790,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -13206,13 +13206,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>1</v>
       </c>
       <c r="U122" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V122" s="10" t="n">
         <v>4</v>
@@ -14636,13 +14636,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>1</v>
@@ -15355,17 +15355,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L143" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-9</v>
+      </c>
+      <c r="L143" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M143" s="8" t="n">
@@ -15666,13 +15666,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -15973,13 +15973,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>0</v>
       </c>
       <c r="V149" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W149" s="9" t="n">
         <v>0</v>
@@ -16293,7 +16293,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -16308,7 +16308,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -16392,7 +16392,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16458,7 +16458,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16557,7 +16557,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16836,7 +16836,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -16854,7 +16854,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17067,7 +17067,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">

--- a/docs/d/26/inyear.xlsx
+++ b/docs/d/26/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 25 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>0</v>
       </c>
       <c r="X14" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y14" s="9" t="n">
         <v>0</v>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="9" t="n">
         <v>0</v>
@@ -2712,13 +2712,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-15</v>
+        <v>-13</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" s="9" t="n">
         <v>0</v>
@@ -3938,13 +3938,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>0</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" s="9" t="n">
         <v>0</v>
@@ -3983,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
@@ -4090,7 +4090,7 @@
         <v>0</v>
       </c>
       <c r="X33" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y33" s="9" t="n">
         <v>0</v>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>4</v>
       </c>
       <c r="W35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" s="10" t="n">
         <v>7</v>
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="P44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="9" t="n">
         <v>0</v>
@@ -5477,13 +5477,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5889,13 +5889,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>0</v>
       </c>
       <c r="Q51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" s="9" t="n">
         <v>0</v>
@@ -6095,13 +6095,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6406,13 +6406,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>1</v>
       </c>
       <c r="U57" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V57" s="9" t="n">
         <v>3</v>
@@ -6919,13 +6919,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q62" s="10" t="n">
         <v>2</v>
@@ -7062,8 +7062,8 @@
       <c r="S62" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T62" s="9" t="n">
-        <v>0</v>
+      <c r="T62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U62" s="9" t="n">
         <v>0</v>
@@ -7933,7 +7933,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7947,13 +7947,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7973,8 +7973,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P71" s="9" t="n">
-        <v>3</v>
+      <c r="P71" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q71" s="9" t="n">
         <v>0</v>
@@ -8183,7 +8183,7 @@
         <v>0</v>
       </c>
       <c r="Q73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" s="9" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8258,13 +8258,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8302,8 +8302,8 @@
       <c r="U74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V74" s="9" t="n">
-        <v>3</v>
+      <c r="V74" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8399,7 +8399,7 @@
         <v>0</v>
       </c>
       <c r="S75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" s="9" t="n">
         <v>0</v>
@@ -8674,13 +8674,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8779,13 +8779,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -10011,13 +10011,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10356,8 +10356,8 @@
       <c r="S94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T94" s="9" t="n">
-        <v>0</v>
+      <c r="T94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U94" s="9" t="n">
         <v>0</v>
@@ -10621,13 +10621,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>1</v>
@@ -11477,7 +11477,7 @@
         <v>0</v>
       </c>
       <c r="S105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T105" s="10" t="n">
         <v>1</v>
@@ -11492,7 +11492,7 @@
         <v>1</v>
       </c>
       <c r="X105" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
@@ -11542,13 +11542,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-15</v>
+        <v>-13</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11643,13 +11643,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>0</v>
       </c>
       <c r="S107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T107" s="10" t="n">
         <v>1</v>
@@ -11688,7 +11688,7 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -11853,13 +11853,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -12273,13 +12273,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12790,13 +12790,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>4</v>
       </c>
       <c r="W118" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X118" s="10" t="n">
         <v>6</v>
@@ -12895,13 +12895,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>4</v>
       </c>
       <c r="W119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X119" s="10" t="n">
         <v>7</v>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13340,8 +13340,8 @@
       <c r="P123" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q123" s="9" t="n">
-        <v>0</v>
+      <c r="Q123" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
@@ -15355,13 +15355,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
@@ -15460,13 +15460,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>0</v>
       </c>
       <c r="V144" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W144" s="9" t="n">
         <v>0</v>
@@ -15565,13 +15565,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16557,13 +16557,13 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -16722,7 +16722,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16920,7 +16920,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
